--- a/test-docs/statistics/statistics.xlsx
+++ b/test-docs/statistics/statistics.xlsx
@@ -18,6 +18,7 @@
     <sheet name="TS-Stat-HourSum" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="TS-Stat-CacheSync" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="TS-Stat-Regression" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="TS-Stat-CronStatReportSync" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Feature Matrix'!$A$2:$J$2</definedName>
@@ -84,7 +85,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -127,6 +128,12 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBE4D5"/>
+        <bgColor rgb="00FBE4D5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -154,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -203,6 +210,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1981,6 +1994,619 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F4B084"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5">
+        <f>HYPERLINK("#'Plan Overview'!A1", "← Back to Plan Overview")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Requirement Ref</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Module/Component</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>TC-STAT-077</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>StatisticReportScheduler — cron fires at 04:00 NSK, ShedLock acquired/released, start/finish markers emit</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Env: ttt-qa-1 (primary) or any env where `ttt.statistic-report.cron` = `0 0 4 * * *` in `application.yml` and ttt-service is deployed.
+ShedLock table accessible via postgres MCP: `SELECT name, lock_until, locked_at, locked_by FROM ttt_backend.shedlock WHERE name = 'StatisticReportScheduler.sync';`.
+Graylog API token for stream `TTT-QA-1` (or TTT-STAGE for stage env).
+No other pod is actively holding the ShedLock row at assertion time.</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>SETUP: Snapshot current `shedlock` row for name `StatisticReportScheduler.sync` — record `lock_until`, `locked_at`.
+SETUP: Snapshot latest Graylog event for marker `"Periodic statistic report sync started..."` on the env's stream (record max timestamp).
+WAIT: Up to 16 h for the next 04:00 NSK boundary. Alternative (preferred for QA): trigger manually via `POST /api/ttt/v1/test/statistic-reports/sync` — the scheduler and the test endpoint both delegate to `StatisticReportScheduler.sync()` / service method, emitting the same markers.
+VERIFY LOG: Graylog `stream:TTT-QA-1 AND message:"Periodic statistic report sync started"` — new event after snapshot timestamp (match exact string including trailing ellipsis `...`).
+VERIFY LOG: Graylog same stream — `message:"Periodic statistic report sync finished."` — paired with the start marker (matching request correlation id if present).
+DB-CHECK: `ttt_backend.shedlock` row `lock_until` advanced past snapshot (lock acquired), and after finish marker, `lock_until` is in the past (lock released — ready for next run).
+CLEANUP: None.</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Start and finish INFO markers appear in sequence on the env's Graylog stream. ShedLock row refreshed (lock_until advanced) during the sync window and released afterward. No concurrent pod re-entered the method while locked.</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>#3423 row 22; EXT-cron-jobs §Session 131.4</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>ttt-service/statistic-report/cron</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>Scheduler and test endpoint share the same service method, so markers are identical. Verify both marker strings EXACTLY — trailing ellipsis on start, trailing period on finish. Matches StatisticReportScheduler.sync() log.info calls verbatim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>TC-STAT-078</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>Delta #8 regression — statistic-report sync failure is logged at INFO level (level:6), NOT ERROR (level:3)</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>Env: ttt-qa-1 with ability to induce a controlled failure in the sync path. One practical route: momentarily break the RabbitMQ connection (drop the `TTT_BACKEND_EMPLOYEE_TOPIC` exchange binding) or exhaust a DB connection pool. Requires infra-team coordination in shared envs — prefer timemachine or a disposable dev env for this test.
+Graylog API token; ability to filter by level (level:3 = ERROR, level:6 = INFO in Graylog's Syslog level mapping).</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>SETUP: Confirm `ttt.statistic-report.cron` active. Snapshot latest `level:3` (ERROR) events on stream.
+SETUP: Induce controlled failure — e.g., revoke DB write permission for the ttt-service DB user on `ttt_backend.statistic_report` for ~60 s, or stop the RabbitMQ broker briefly (infra coordination required).
+TRIGGER: `POST /api/ttt/v1/test/statistic-reports/sync` (expect non-200 OR silent swallow — scheduler catches and logs).
+WAIT: 5 s for log propagation.
+VERIFY LOG (negative): Graylog `stream:TTT-QA-1 AND level:3 AND message:"statistic report"` — NO new ERROR events. This is the regression assertion — if ERROR events appear, the bug was accidentally fixed and this TC must be re-triaged.
+VERIFY LOG (positive): Graylog same stream `level:6 AND message:"Periodic statistic report sync failed with cause"` — new INFO event captured after trigger with the exception detail in the cause payload.
+CLEANUP: Restore DB permissions / RabbitMQ broker. Trigger the endpoint again to confirm success marker returns.</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>Failure event is emitted at INFO level (level:6) with the literal prefix `Periodic statistic report sync failed with cause: `. NO event at ERROR level (level:3) for the same failure. Alerting rules watching `level:3 AND message:"statistic report"` would not fire — this is the design issue, and this TC acts as a regression guard in case a future patch "fixes" it by elevating to ERROR (which would require updating alerting rules too).</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="inlineStr">
+        <is>
+          <t>#3423 row 22; Delta #8; EXT-cron-jobs §Session 131.4 Bug</t>
+        </is>
+      </c>
+      <c r="I5" s="22" t="inlineStr">
+        <is>
+          <t>ttt-service/statistic-report/logging</t>
+        </is>
+      </c>
+      <c r="J5" s="22" t="inlineStr">
+        <is>
+          <t>Ticket body flags this as a design issue, not a defect to be fixed right now. The TC exists to detect silent behavior changes on either side (INFO→ERROR or ERROR→INFO). Needs infra support to reliably induce failure — if skipped in CI, run manually during regression passes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>TC-STAT-079</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>#3345 Bug 1 regression — employment-period filter excludes pre-hire and post-leave months</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Env: ttt-qa-1 with at least 2 employees having non-trivial `employee_period` ranges (one hired mid-year, one dismissed mid-year). Reference data from #3345 QA: omaksimova hired 2025-09-01; jsaidov dismissed 2025-11-12. If those specific employees are not on the env, pick equivalents:
+  SELECT e.login, ep.start_date, ep.end_date
+  FROM ttt_backend.employee e
+  JOIN ttt_vacation.employee_period ep ON ep.employee_id = e.id
+  WHERE ep.start_date &gt; (CURRENT_DATE - INTERVAL '12 months')
+    OR ep.end_date BETWEEN (CURRENT_DATE - INTERVAL '12 months') AND CURRENT_DATE
+  LIMIT 10;
+Pick one pre-hire and one post-leave candidate.</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>SETUP: Record candidate employees' login, id, start_date, end_date.
+TRIGGER: `POST /api/ttt/v1/test/statistic-reports/full-sync` (full sync — covers previous + current year scope).
+WAIT: 120 s for RabbitMQ event fan-out to complete (async contract per [[3262-ticket-findings]] §3D note 5).
+DB-CHECK (pre-hire employee): `SELECT count(*) FROM ttt_backend.statistic_report sr WHERE sr.employee_id = &lt;id&gt; AND sr.month_start &lt; '&lt;start_date-month&gt;';` → must be 0. Confirms no rows exist for months before the employee was hired.
+DB-CHECK (post-leave employee): `SELECT count(*) FROM ttt_backend.statistic_report sr WHERE sr.employee_id = &lt;id&gt; AND sr.month_start &gt; '&lt;end_date-month&gt;';` → must be 0. Confirms no rows exist for months after the employee left.
+DB-CHECK (sanity — in-period rows present): `SELECT count(*) FROM ttt_backend.statistic_report sr WHERE sr.employee_id = &lt;id&gt; AND sr.month_start BETWEEN '&lt;start_date-month&gt;' AND COALESCE('&lt;end_date-month&gt;', CURRENT_DATE);` → must be &gt; 0 (sync produced in-period rows — otherwise the whole sync failed silently).
+CLEANUP: None.</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>For pre-hire employee: statistic_report has zero rows before start_date month. For post-leave employee: zero rows after end_date month. In-period rows exist (sync worked). Regression for bug fixed in !5101 — before the fix, pre-hire and post-leave rows were incorrectly persisted.</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>#3345 Bug 1 (MR !5101); #3423 row 22</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>ttt-service/statistic-report/sync</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>Mid-month hire/leave edge case remains open as #3356 — currently any month in which the employee was employed ANY day is included. This TC is month-granularity, not day-granularity, so it does not exercise the #3356 boundary. Do NOT tighten assertions to include/exclude partial months without coordinating with #3356.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>TC-STAT-080</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>#3345 Bug 2 regression — day-off reschedule triggers month_norm recalculation via RabbitMQ event</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>Env: ttt-qa-1. Active employee with at least one existing day-off in the current or next month whose reschedule can be tested without affecting live data.
+Query:
+  SELECT d.id, d.employee_id, e.login, d.day, d.day_off_type
+  FROM ttt_vacation.day_off d
+  JOIN ttt_backend.employee e ON e.id = d.employee_id
+  WHERE d.day &gt;= CURRENT_DATE
+    AND d.day &lt; CURRENT_DATE + INTERVAL '60 days'
+    AND e.enabled = true
+  ORDER BY random() LIMIT 1;
+RabbitMQ `TTT_BACKEND_EMPLOYEE_TOPIC` healthy and consumer bound on routing `employee-month-norm-context-calculated`.</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>SETUP: Record chosen day-off id, employee_id, login, original day, day_off_type.
+SETUP: Snapshot `month_norm` for the affected month: `SELECT month_norm FROM ttt_backend.statistic_report WHERE employee_id = &lt;emp_id&gt; AND month_start = date_trunc('month', '&lt;original_day&gt;'::date);` → record as `norm_before`.
+TRIGGER (UI-first): Log into TTT as the employee or a permitted manager. Navigate to Calendar → Day-off page. Reschedule the day-off to a date within the same month (e.g., move from the 10th to the 11th). Confirm reschedule via UI.
+  Alternative (API): `PATCH /api/vacation/v1/day-offs/&lt;id&gt;` with new `day` field.
+WAIT: 60 s for the RabbitMQ event to propagate (routing `employee-month-norm-context-calculated`; StatisticReportUpdateEventType.VACATION_CHANGES fires).
+DB-CHECK: `SELECT month_norm FROM ttt_backend.statistic_report WHERE employee_id = &lt;emp_id&gt; AND month_start = date_trunc('month', '&lt;new_day&gt;'::date);` → record as `norm_after`. Value must be recomputed (can be equal to `norm_before` if both days are workdays with the same hours; in that case, verify the `updated_at` column advanced to confirm the row was touched).
+VERIFY LOG: Graylog — event with routing `employee-month-norm-context-calculated` emitted within 60 s window after trigger.
+CLEANUP: Restore day-off to original date via UI or API.</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>`statistic_report.month_norm` OR `updated_at` reflects the day-off reschedule. RabbitMQ event fired on the employee-norm routing within 60 s. Before the #3345 fix, this did nothing (event was not wired); the TC guards against that regression.</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="inlineStr">
+        <is>
+          <t>#3345 Bug 2; #3423 row 22</t>
+        </is>
+      </c>
+      <c r="I7" s="22" t="inlineStr">
+        <is>
+          <t>ttt-service/statistic-report/event-handler</t>
+        </is>
+      </c>
+      <c r="J7" s="22" t="inlineStr">
+        <is>
+          <t>If both original and new day are workdays with identical norm-hour semantics, month_norm might not change numerically — in that case, asserting on updated_at advancing is the primary signal. Use a cross-month reschedule (e.g., from Sept 30 to Oct 1) for stronger numerical assertions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>TC-STAT-081</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>#3337 regression — sick-leave creation updates month_norm and reported_effort via SICK_LEAVE_CHANGES event</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Env: ttt-qa-1. Employee without a sick-leave in the target month, with at least 3 working days available in that month for a synthetic sick-leave.
+Query:
+  SELECT e.id, e.login
+  FROM ttt_backend.employee e
+  WHERE e.enabled = true
+    AND NOT EXISTS (
+      SELECT 1 FROM ttt_vacation.sick_leave sl
+      WHERE sl.employee_id = e.id
+        AND sl.start_date &gt;= date_trunc('month', CURRENT_DATE)
+        AND sl.start_date &lt; date_trunc('month', CURRENT_DATE) + INTERVAL '1 month'
+    )
+  ORDER BY random() LIMIT 1;
+RabbitMQ healthy.</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>SETUP: Record employee id, login, target month.
+SETUP: Snapshot stat-report row: `SELECT month_norm, reported_effort, updated_at FROM ttt_backend.statistic_report WHERE employee_id = &lt;id&gt; AND month_start = date_trunc('month', CURRENT_DATE);`.
+SETUP (create sick-leave via API): `POST /api/vacation/v1/sick-leaves` body `{"login": "&lt;login&gt;", "startDate": "&lt;today&gt;", "endDate": "&lt;today+2&gt;", "type": "PERSONAL"}`. Record new sick-leave id.
+WAIT: 60 s for RabbitMQ fan-out (StatisticReportUpdateEventType.SICK_LEAVE_CHANGES).
+DB-CHECK: Re-query the stat-report row — `updated_at` must advance past snapshot. `month_norm` should decrease by the working-day-hours covered by the sick-leave (typically 3 days × 8 h = 24 h, but depends on office production calendar). `reported_effort` may be unchanged (sick-leave itself is not a task report) or reduced per business rule.
+VERIFY LOG: Graylog — sick-leave service logs the event emit; routing `employee-month-norm-context-calculated` fired.
+CLEANUP (via API): `DELETE /api/vacation/v1/sick-leaves/&lt;new_id&gt;`. Re-check stat-report row — `updated_at` advances again, `month_norm` restored to snapshot value.</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Sick-leave creation triggers the stat-report row refresh within 60 s; `updated_at` advances; `month_norm` decreases by the expected working hours. Regression for the #3337 pre-fix state where sick-leave events did not propagate.</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>#3337 (sick-leave month_norm propagation); #3423 row 22</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>ttt-service/statistic-report/event-handler</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>If allow_api_mutations is false in config.yaml, this TC is blocked — document as SKIPPED in the run. Requires either a dev env with mutations enabled or full manual execution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>TC-STAT-082</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>#3337 regression — scoped event for employee A does NOT delete statistic_report rows for employee B</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>Env: ttt-qa-1. Two distinct active employees A and B, each with existing `statistic_report` rows for current and previous month. Employees must be unrelated (different offices, different projects, different managers) to ensure no shared event fan-out by coincidence.
+Query:
+  SELECT e.id, e.login, e.office_id, e.manager_id
+  FROM ttt_backend.employee e
+  WHERE e.enabled = true
+    AND EXISTS (
+      SELECT 1 FROM ttt_backend.statistic_report sr
+      WHERE sr.employee_id = e.id
+        AND sr.month_start &gt;= date_trunc('month', CURRENT_DATE - INTERVAL '1 month')
+    )
+  ORDER BY random() LIMIT 5;
+Pick A and B with different office_id and different manager_id.</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>SETUP: Record employee A and B details. Snapshot employee B's stat-report rows: `SELECT month_start, month_norm, reported_effort, updated_at FROM ttt_backend.statistic_report WHERE employee_id = &lt;B_id&gt; ORDER BY month_start;` — save full resultset as `B_snapshot`.
+TRIGGER: Cause a scoped event for employee A ONLY. Options:
+  (a) Create a task_report for A via UI or `POST /api/ttt/v1/task-reports`.
+  (b) Update A's day-off (see TC-STAT-080 steps).
+  (c) Add a sick-leave for A (see TC-STAT-081 steps).
+WAIT: 90 s for full event propagation and fan-out.
+DB-CHECK (primary): Re-query employee B's stat-report rows with identical SQL — must equal `B_snapshot` exactly (same count of rows, same month_norm, same reported_effort, same updated_at timestamps — B's rows were NOT touched).
+DB-CHECK (sanity): Employee A's stat-report row for the affected month was refreshed (updated_at advanced) — confirms the event delivery path works; it's the SCOPING that's under test, not fan-out itself.
+CLEANUP: Revert the trigger mutation (delete the test task_report / sick-leave, restore day-off).</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>Employee B's statistic_report rows are IDENTICAL before and after the trigger (updated_at unchanged). Employee A's row for the affected month was refreshed. Regression for the #3337 bug where a bulk recalc incorrectly deleted unrelated rows — the fix scoped the DELETE to `employee_id IN (changed_set)`, and this TC guards against that scoping regressing to an unscoped delete.</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>#3337 (scoped delete fix); #3423 row 22</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>ttt-service/statistic-report/event-handler</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="inlineStr">
+        <is>
+          <t>The more employee B differs from A (different office, manager, department), the stronger this TC's coverage. Picking two employees from the same project weakens the test because their events may legitimately fan out together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>TC-STAT-083</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>#3346 regression (bug #895498) — manual statistic_report row delete is restored on next optimized sync</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Env: ttt-qa-1. Active employee with a statistic_report row for current month that can be temporarily deleted and restored. Choose an employee unlikely to view their statistics during the test window (avoid disrupting QA's own reports page).
+DB write access to `ttt_backend.statistic_report` required.
+Query candidate:
+  SELECT sr.id, sr.employee_id, e.login, sr.month_start
+  FROM ttt_backend.statistic_report sr
+  JOIN ttt_backend.employee e ON e.id = sr.employee_id
+  WHERE sr.month_start = date_trunc('month', CURRENT_DATE)
+    AND e.enabled = true
+  ORDER BY random() LIMIT 1;</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>SETUP: Record candidate row — full SELECT of all columns. Save as `deleted_snapshot`.
+TRIGGER (destructive): `DELETE FROM ttt_backend.statistic_report WHERE id = &lt;row_id&gt;;` via postgres MCP.
+DB-CHECK (precondition): Re-query for the row — must be absent (delete succeeded).
+TRIGGER (sync): `POST /api/ttt/v1/test/statistic-reports/sync` (optimized sync — previous + current month scope).
+WAIT: 120 s for RabbitMQ fan-out (StatisticReportUpdateEventType.INITIAL_SYNC on the affected employee).
+DB-CHECK (primary): Row reappears — `SELECT * FROM ttt_backend.statistic_report WHERE employee_id = &lt;emp_id&gt; AND month_start = '&lt;current_month_start&gt;'::date;` returns exactly one row. Columns match `deleted_snapshot` (id may differ — verify month_norm, reported_effort, employee_id).
+VERIFY LOG: Graylog — `"Periodic statistic report sync finished."` marker fired between trigger and row reappearance.
+CLEANUP: No additional cleanup needed — the row is fully regenerated. If numerical values differ from snapshot, investigate (they should match within the event-consistency window).</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Periodic sync restores the deleted row. Regression for bug #895498 (pre-#3346 fix) where the scheduler was not wired, so deleted rows stayed deleted until a restart. Also validates the idempotency contract — sync should be safe to rerun.</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>#3346 bug #895498; #3423 row 22</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>ttt-service/statistic-report/sync</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>The full-sync endpoint `/api/ttt/v1/test/statistic-reports/full-sync` would also restore the row but covers a wider year scope; use optimized sync here to exercise the minimum-coverage path. Requires DB write access — runs on non-shared envs preferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>TC-STAT-084</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>Full vs optimized sync contract — full refreshes previous + current year; optimized refreshes previous + current month only</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>Env: ttt-qa-1 with `statistic_report` populated for at least the past 12 months across a sample of employees. Access to the two test endpoints:
+  POST /api/ttt/v1/test/statistic-reports/full-sync     (full)
+  POST /api/ttt/v1/test/statistic-reports/sync          (optimized)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>SETUP: Snapshot `max(updated_at)` per month for an employee with a full year of data:
+  SELECT month_start, max(updated_at) as last_updated
+  FROM ttt_backend.statistic_report
+  WHERE employee_id = &lt;chosen_emp_id&gt;
+  GROUP BY month_start ORDER BY month_start;
+Record as `snapshot_before_optimized`.
+TRIGGER (optimized): `POST /api/ttt/v1/test/statistic-reports/sync`.
+WAIT: 120 s.
+DB-CHECK (optimized scope): Re-query same SQL. Only rows for `date_trunc('month', CURRENT_DATE)` and `date_trunc('month', CURRENT_DATE - INTERVAL '1 month')` should have `updated_at` advanced; all OLDER month rows unchanged.
+SETUP (reset snapshot): Re-snapshot as `snapshot_before_full`.
+TRIGGER (full): `POST /api/ttt/v1/test/statistic-reports/full-sync`.
+WAIT: 300 s (full sync is slower — year scope).
+DB-CHECK (full scope): Re-query. ALL rows for `date_trunc('year', CURRENT_DATE)` and `date_trunc('year', CURRENT_DATE - INTERVAL '1 year')` should have `updated_at` advanced; rows older than 2 years unchanged.
+CLEANUP: None.</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>Optimized sync updates previous + current month rows only. Full sync updates previous + current year rows (all 12–24 months in the year scope). Rows outside each scope remain untouched (`updated_at` preserved). Confirms the two endpoints have distinct, documented effects — critical for QA's data-setup playbooks (which endpoint to call to refresh what).</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>#3345 note 894873; #3423 row 22; EXT-cron-jobs §Session 131.4</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>ttt-service/statistic-report/sync</t>
+        </is>
+      </c>
+      <c r="J11" s="22" t="inlineStr">
+        <is>
+          <t>Per #3345 note 894895 (omaksimova 2026-01-07), full-sync 'NOT-A-BUG' observation: dismissed employees briefly appeared in current-year records after full sync because the scope includes them by definition. Expected behavior — do NOT assert dismissed-employee absence in full-sync scope. That assertion belongs in TC-STAT-079 (post-leave filter) only.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/test-docs/statistics/statistics.xlsx
+++ b/test-docs/statistics/statistics.xlsx
@@ -18,7 +18,6 @@
     <sheet name="TS-Stat-HourSum" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="TS-Stat-CacheSync" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="TS-Stat-Regression" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="TS-Stat-CronStatReportSync" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Feature Matrix'!$A$2:$J$2</definedName>
@@ -1994,619 +1993,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F4B084"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="35" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5">
-        <f>HYPERLINK("#'Plan Overview'!A1", "← Back to Plan Overview")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>Test ID</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>Preconditions</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>Requirement Ref</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>Module/Component</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>TC-STAT-077</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>StatisticReportScheduler — cron fires at 04:00 NSK, ShedLock acquired/released, start/finish markers emit</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Env: ttt-qa-1 (primary) or any env where `ttt.statistic-report.cron` = `0 0 4 * * *` in `application.yml` and ttt-service is deployed.
-ShedLock table accessible via postgres MCP: `SELECT name, lock_until, locked_at, locked_by FROM ttt_backend.shedlock WHERE name = 'StatisticReportScheduler.sync';`.
-Graylog API token for stream `TTT-QA-1` (or TTT-STAGE for stage env).
-No other pod is actively holding the ShedLock row at assertion time.</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>SETUP: Snapshot current `shedlock` row for name `StatisticReportScheduler.sync` — record `lock_until`, `locked_at`.
-SETUP: Snapshot latest Graylog event for marker `"Periodic statistic report sync started..."` on the env's stream (record max timestamp).
-WAIT: Up to 16 h for the next 04:00 NSK boundary. Alternative (preferred for QA): trigger manually via `POST /api/ttt/v1/test/statistic-reports/sync` — the scheduler and the test endpoint both delegate to `StatisticReportScheduler.sync()` / service method, emitting the same markers.
-VERIFY LOG: Graylog `stream:TTT-QA-1 AND message:"Periodic statistic report sync started"` — new event after snapshot timestamp (match exact string including trailing ellipsis `...`).
-VERIFY LOG: Graylog same stream — `message:"Periodic statistic report sync finished."` — paired with the start marker (matching request correlation id if present).
-DB-CHECK: `ttt_backend.shedlock` row `lock_until` advanced past snapshot (lock acquired), and after finish marker, `lock_until` is in the past (lock released — ready for next run).
-CLEANUP: None.</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Start and finish INFO markers appear in sequence on the env's Graylog stream. ShedLock row refreshed (lock_until advanced) during the sync window and released afterward. No concurrent pod re-entered the method while locked.</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="G4" s="10" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>#3423 row 22; EXT-cron-jobs §Session 131.4</t>
-        </is>
-      </c>
-      <c r="I4" s="8" t="inlineStr">
-        <is>
-          <t>ttt-service/statistic-report/cron</t>
-        </is>
-      </c>
-      <c r="J4" s="8" t="inlineStr">
-        <is>
-          <t>Scheduler and test endpoint share the same service method, so markers are identical. Verify both marker strings EXACTLY — trailing ellipsis on start, trailing period on finish. Matches StatisticReportScheduler.sync() log.info calls verbatim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="21" t="inlineStr">
-        <is>
-          <t>TC-STAT-078</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="inlineStr">
-        <is>
-          <t>Delta #8 regression — statistic-report sync failure is logged at INFO level (level:6), NOT ERROR (level:3)</t>
-        </is>
-      </c>
-      <c r="C5" s="22" t="inlineStr">
-        <is>
-          <t>Env: ttt-qa-1 with ability to induce a controlled failure in the sync path. One practical route: momentarily break the RabbitMQ connection (drop the `TTT_BACKEND_EMPLOYEE_TOPIC` exchange binding) or exhaust a DB connection pool. Requires infra-team coordination in shared envs — prefer timemachine or a disposable dev env for this test.
-Graylog API token; ability to filter by level (level:3 = ERROR, level:6 = INFO in Graylog's Syslog level mapping).</t>
-        </is>
-      </c>
-      <c r="D5" s="22" t="inlineStr">
-        <is>
-          <t>SETUP: Confirm `ttt.statistic-report.cron` active. Snapshot latest `level:3` (ERROR) events on stream.
-SETUP: Induce controlled failure — e.g., revoke DB write permission for the ttt-service DB user on `ttt_backend.statistic_report` for ~60 s, or stop the RabbitMQ broker briefly (infra coordination required).
-TRIGGER: `POST /api/ttt/v1/test/statistic-reports/sync` (expect non-200 OR silent swallow — scheduler catches and logs).
-WAIT: 5 s for log propagation.
-VERIFY LOG (negative): Graylog `stream:TTT-QA-1 AND level:3 AND message:"statistic report"` — NO new ERROR events. This is the regression assertion — if ERROR events appear, the bug was accidentally fixed and this TC must be re-triaged.
-VERIFY LOG (positive): Graylog same stream `level:6 AND message:"Periodic statistic report sync failed with cause"` — new INFO event captured after trigger with the exception detail in the cause payload.
-CLEANUP: Restore DB permissions / RabbitMQ broker. Trigger the endpoint again to confirm success marker returns.</t>
-        </is>
-      </c>
-      <c r="E5" s="22" t="inlineStr">
-        <is>
-          <t>Failure event is emitted at INFO level (level:6) with the literal prefix `Periodic statistic report sync failed with cause: `. NO event at ERROR level (level:3) for the same failure. Alerting rules watching `level:3 AND message:"statistic report"` would not fire — this is the design issue, and this TC acts as a regression guard in case a future patch "fixes" it by elevating to ERROR (which would require updating alerting rules too).</t>
-        </is>
-      </c>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G5" s="21" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="H5" s="22" t="inlineStr">
-        <is>
-          <t>#3423 row 22; Delta #8; EXT-cron-jobs §Session 131.4 Bug</t>
-        </is>
-      </c>
-      <c r="I5" s="22" t="inlineStr">
-        <is>
-          <t>ttt-service/statistic-report/logging</t>
-        </is>
-      </c>
-      <c r="J5" s="22" t="inlineStr">
-        <is>
-          <t>Ticket body flags this as a design issue, not a defect to be fixed right now. The TC exists to detect silent behavior changes on either side (INFO→ERROR or ERROR→INFO). Needs infra support to reliably induce failure — if skipped in CI, run manually during regression passes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>TC-STAT-079</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>#3345 Bug 1 regression — employment-period filter excludes pre-hire and post-leave months</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Env: ttt-qa-1 with at least 2 employees having non-trivial `employee_period` ranges (one hired mid-year, one dismissed mid-year). Reference data from #3345 QA: omaksimova hired 2025-09-01; jsaidov dismissed 2025-11-12. If those specific employees are not on the env, pick equivalents:
-  SELECT e.login, ep.start_date, ep.end_date
-  FROM ttt_backend.employee e
-  JOIN ttt_vacation.employee_period ep ON ep.employee_id = e.id
-  WHERE ep.start_date &gt; (CURRENT_DATE - INTERVAL '12 months')
-    OR ep.end_date BETWEEN (CURRENT_DATE - INTERVAL '12 months') AND CURRENT_DATE
-  LIMIT 10;
-Pick one pre-hire and one post-leave candidate.</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>SETUP: Record candidate employees' login, id, start_date, end_date.
-TRIGGER: `POST /api/ttt/v1/test/statistic-reports/full-sync` (full sync — covers previous + current year scope).
-WAIT: 120 s for RabbitMQ event fan-out to complete (async contract per [[3262-ticket-findings]] §3D note 5).
-DB-CHECK (pre-hire employee): `SELECT count(*) FROM ttt_backend.statistic_report sr WHERE sr.employee_id = &lt;id&gt; AND sr.month_start &lt; '&lt;start_date-month&gt;';` → must be 0. Confirms no rows exist for months before the employee was hired.
-DB-CHECK (post-leave employee): `SELECT count(*) FROM ttt_backend.statistic_report sr WHERE sr.employee_id = &lt;id&gt; AND sr.month_start &gt; '&lt;end_date-month&gt;';` → must be 0. Confirms no rows exist for months after the employee left.
-DB-CHECK (sanity — in-period rows present): `SELECT count(*) FROM ttt_backend.statistic_report sr WHERE sr.employee_id = &lt;id&gt; AND sr.month_start BETWEEN '&lt;start_date-month&gt;' AND COALESCE('&lt;end_date-month&gt;', CURRENT_DATE);` → must be &gt; 0 (sync produced in-period rows — otherwise the whole sync failed silently).
-CLEANUP: None.</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>For pre-hire employee: statistic_report has zero rows before start_date month. For post-leave employee: zero rows after end_date month. In-period rows exist (sync worked). Regression for bug fixed in !5101 — before the fix, pre-hire and post-leave rows were incorrectly persisted.</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>#3345 Bug 1 (MR !5101); #3423 row 22</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>ttt-service/statistic-report/sync</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>Mid-month hire/leave edge case remains open as #3356 — currently any month in which the employee was employed ANY day is included. This TC is month-granularity, not day-granularity, so it does not exercise the #3356 boundary. Do NOT tighten assertions to include/exclude partial months without coordinating with #3356.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="21" t="inlineStr">
-        <is>
-          <t>TC-STAT-080</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>#3345 Bug 2 regression — day-off reschedule triggers month_norm recalculation via RabbitMQ event</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>Env: ttt-qa-1. Active employee with at least one existing day-off in the current or next month whose reschedule can be tested without affecting live data.
-Query:
-  SELECT d.id, d.employee_id, e.login, d.day, d.day_off_type
-  FROM ttt_vacation.day_off d
-  JOIN ttt_backend.employee e ON e.id = d.employee_id
-  WHERE d.day &gt;= CURRENT_DATE
-    AND d.day &lt; CURRENT_DATE + INTERVAL '60 days'
-    AND e.enabled = true
-  ORDER BY random() LIMIT 1;
-RabbitMQ `TTT_BACKEND_EMPLOYEE_TOPIC` healthy and consumer bound on routing `employee-month-norm-context-calculated`.</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>SETUP: Record chosen day-off id, employee_id, login, original day, day_off_type.
-SETUP: Snapshot `month_norm` for the affected month: `SELECT month_norm FROM ttt_backend.statistic_report WHERE employee_id = &lt;emp_id&gt; AND month_start = date_trunc('month', '&lt;original_day&gt;'::date);` → record as `norm_before`.
-TRIGGER (UI-first): Log into TTT as the employee or a permitted manager. Navigate to Calendar → Day-off page. Reschedule the day-off to a date within the same month (e.g., move from the 10th to the 11th). Confirm reschedule via UI.
-  Alternative (API): `PATCH /api/vacation/v1/day-offs/&lt;id&gt;` with new `day` field.
-WAIT: 60 s for the RabbitMQ event to propagate (routing `employee-month-norm-context-calculated`; StatisticReportUpdateEventType.VACATION_CHANGES fires).
-DB-CHECK: `SELECT month_norm FROM ttt_backend.statistic_report WHERE employee_id = &lt;emp_id&gt; AND month_start = date_trunc('month', '&lt;new_day&gt;'::date);` → record as `norm_after`. Value must be recomputed (can be equal to `norm_before` if both days are workdays with the same hours; in that case, verify the `updated_at` column advanced to confirm the row was touched).
-VERIFY LOG: Graylog — event with routing `employee-month-norm-context-calculated` emitted within 60 s window after trigger.
-CLEANUP: Restore day-off to original date via UI or API.</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="inlineStr">
-        <is>
-          <t>`statistic_report.month_norm` OR `updated_at` reflects the day-off reschedule. RabbitMQ event fired on the employee-norm routing within 60 s. Before the #3345 fix, this did nothing (event was not wired); the TC guards against that regression.</t>
-        </is>
-      </c>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="H7" s="22" t="inlineStr">
-        <is>
-          <t>#3345 Bug 2; #3423 row 22</t>
-        </is>
-      </c>
-      <c r="I7" s="22" t="inlineStr">
-        <is>
-          <t>ttt-service/statistic-report/event-handler</t>
-        </is>
-      </c>
-      <c r="J7" s="22" t="inlineStr">
-        <is>
-          <t>If both original and new day are workdays with identical norm-hour semantics, month_norm might not change numerically — in that case, asserting on updated_at advancing is the primary signal. Use a cross-month reschedule (e.g., from Sept 30 to Oct 1) for stronger numerical assertions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>TC-STAT-081</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>#3337 regression — sick-leave creation updates month_norm and reported_effort via SICK_LEAVE_CHANGES event</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Env: ttt-qa-1. Employee without a sick-leave in the target month, with at least 3 working days available in that month for a synthetic sick-leave.
-Query:
-  SELECT e.id, e.login
-  FROM ttt_backend.employee e
-  WHERE e.enabled = true
-    AND NOT EXISTS (
-      SELECT 1 FROM ttt_vacation.sick_leave sl
-      WHERE sl.employee_id = e.id
-        AND sl.start_date &gt;= date_trunc('month', CURRENT_DATE)
-        AND sl.start_date &lt; date_trunc('month', CURRENT_DATE) + INTERVAL '1 month'
-    )
-  ORDER BY random() LIMIT 1;
-RabbitMQ healthy.</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>SETUP: Record employee id, login, target month.
-SETUP: Snapshot stat-report row: `SELECT month_norm, reported_effort, updated_at FROM ttt_backend.statistic_report WHERE employee_id = &lt;id&gt; AND month_start = date_trunc('month', CURRENT_DATE);`.
-SETUP (create sick-leave via API): `POST /api/vacation/v1/sick-leaves` body `{"login": "&lt;login&gt;", "startDate": "&lt;today&gt;", "endDate": "&lt;today+2&gt;", "type": "PERSONAL"}`. Record new sick-leave id.
-WAIT: 60 s for RabbitMQ fan-out (StatisticReportUpdateEventType.SICK_LEAVE_CHANGES).
-DB-CHECK: Re-query the stat-report row — `updated_at` must advance past snapshot. `month_norm` should decrease by the working-day-hours covered by the sick-leave (typically 3 days × 8 h = 24 h, but depends on office production calendar). `reported_effort` may be unchanged (sick-leave itself is not a task report) or reduced per business rule.
-VERIFY LOG: Graylog — sick-leave service logs the event emit; routing `employee-month-norm-context-calculated` fired.
-CLEANUP (via API): `DELETE /api/vacation/v1/sick-leaves/&lt;new_id&gt;`. Re-check stat-report row — `updated_at` advances again, `month_norm` restored to snapshot value.</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>Sick-leave creation triggers the stat-report row refresh within 60 s; `updated_at` advances; `month_norm` decreases by the expected working hours. Regression for the #3337 pre-fix state where sick-leave events did not propagate.</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>#3337 (sick-leave month_norm propagation); #3423 row 22</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>ttt-service/statistic-report/event-handler</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>If allow_api_mutations is false in config.yaml, this TC is blocked — document as SKIPPED in the run. Requires either a dev env with mutations enabled or full manual execution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="21" t="inlineStr">
-        <is>
-          <t>TC-STAT-082</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>#3337 regression — scoped event for employee A does NOT delete statistic_report rows for employee B</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
-        <is>
-          <t>Env: ttt-qa-1. Two distinct active employees A and B, each with existing `statistic_report` rows for current and previous month. Employees must be unrelated (different offices, different projects, different managers) to ensure no shared event fan-out by coincidence.
-Query:
-  SELECT e.id, e.login, e.office_id, e.manager_id
-  FROM ttt_backend.employee e
-  WHERE e.enabled = true
-    AND EXISTS (
-      SELECT 1 FROM ttt_backend.statistic_report sr
-      WHERE sr.employee_id = e.id
-        AND sr.month_start &gt;= date_trunc('month', CURRENT_DATE - INTERVAL '1 month')
-    )
-  ORDER BY random() LIMIT 5;
-Pick A and B with different office_id and different manager_id.</t>
-        </is>
-      </c>
-      <c r="D9" s="22" t="inlineStr">
-        <is>
-          <t>SETUP: Record employee A and B details. Snapshot employee B's stat-report rows: `SELECT month_start, month_norm, reported_effort, updated_at FROM ttt_backend.statistic_report WHERE employee_id = &lt;B_id&gt; ORDER BY month_start;` — save full resultset as `B_snapshot`.
-TRIGGER: Cause a scoped event for employee A ONLY. Options:
-  (a) Create a task_report for A via UI or `POST /api/ttt/v1/task-reports`.
-  (b) Update A's day-off (see TC-STAT-080 steps).
-  (c) Add a sick-leave for A (see TC-STAT-081 steps).
-WAIT: 90 s for full event propagation and fan-out.
-DB-CHECK (primary): Re-query employee B's stat-report rows with identical SQL — must equal `B_snapshot` exactly (same count of rows, same month_norm, same reported_effort, same updated_at timestamps — B's rows were NOT touched).
-DB-CHECK (sanity): Employee A's stat-report row for the affected month was refreshed (updated_at advanced) — confirms the event delivery path works; it's the SCOPING that's under test, not fan-out itself.
-CLEANUP: Revert the trigger mutation (delete the test task_report / sick-leave, restore day-off).</t>
-        </is>
-      </c>
-      <c r="E9" s="22" t="inlineStr">
-        <is>
-          <t>Employee B's statistic_report rows are IDENTICAL before and after the trigger (updated_at unchanged). Employee A's row for the affected month was refreshed. Regression for the #3337 bug where a bulk recalc incorrectly deleted unrelated rows — the fix scoped the DELETE to `employee_id IN (changed_set)`, and this TC guards against that scoping regressing to an unscoped delete.</t>
-        </is>
-      </c>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G9" s="21" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="H9" s="22" t="inlineStr">
-        <is>
-          <t>#3337 (scoped delete fix); #3423 row 22</t>
-        </is>
-      </c>
-      <c r="I9" s="22" t="inlineStr">
-        <is>
-          <t>ttt-service/statistic-report/event-handler</t>
-        </is>
-      </c>
-      <c r="J9" s="22" t="inlineStr">
-        <is>
-          <t>The more employee B differs from A (different office, manager, department), the stronger this TC's coverage. Picking two employees from the same project weakens the test because their events may legitimately fan out together.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>TC-STAT-083</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>#3346 regression (bug #895498) — manual statistic_report row delete is restored on next optimized sync</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Env: ttt-qa-1. Active employee with a statistic_report row for current month that can be temporarily deleted and restored. Choose an employee unlikely to view their statistics during the test window (avoid disrupting QA's own reports page).
-DB write access to `ttt_backend.statistic_report` required.
-Query candidate:
-  SELECT sr.id, sr.employee_id, e.login, sr.month_start
-  FROM ttt_backend.statistic_report sr
-  JOIN ttt_backend.employee e ON e.id = sr.employee_id
-  WHERE sr.month_start = date_trunc('month', CURRENT_DATE)
-    AND e.enabled = true
-  ORDER BY random() LIMIT 1;</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>SETUP: Record candidate row — full SELECT of all columns. Save as `deleted_snapshot`.
-TRIGGER (destructive): `DELETE FROM ttt_backend.statistic_report WHERE id = &lt;row_id&gt;;` via postgres MCP.
-DB-CHECK (precondition): Re-query for the row — must be absent (delete succeeded).
-TRIGGER (sync): `POST /api/ttt/v1/test/statistic-reports/sync` (optimized sync — previous + current month scope).
-WAIT: 120 s for RabbitMQ fan-out (StatisticReportUpdateEventType.INITIAL_SYNC on the affected employee).
-DB-CHECK (primary): Row reappears — `SELECT * FROM ttt_backend.statistic_report WHERE employee_id = &lt;emp_id&gt; AND month_start = '&lt;current_month_start&gt;'::date;` returns exactly one row. Columns match `deleted_snapshot` (id may differ — verify month_norm, reported_effort, employee_id).
-VERIFY LOG: Graylog — `"Periodic statistic report sync finished."` marker fired between trigger and row reappearance.
-CLEANUP: No additional cleanup needed — the row is fully regenerated. If numerical values differ from snapshot, investigate (they should match within the event-consistency window).</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>Periodic sync restores the deleted row. Regression for bug #895498 (pre-#3346 fix) where the scheduler was not wired, so deleted rows stayed deleted until a restart. Also validates the idempotency contract — sync should be safe to rerun.</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>#3346 bug #895498; #3423 row 22</t>
-        </is>
-      </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>ttt-service/statistic-report/sync</t>
-        </is>
-      </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t>The full-sync endpoint `/api/ttt/v1/test/statistic-reports/full-sync` would also restore the row but covers a wider year scope; use optimized sync here to exercise the minimum-coverage path. Requires DB write access — runs on non-shared envs preferred.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="21" t="inlineStr">
-        <is>
-          <t>TC-STAT-084</t>
-        </is>
-      </c>
-      <c r="B11" s="22" t="inlineStr">
-        <is>
-          <t>Full vs optimized sync contract — full refreshes previous + current year; optimized refreshes previous + current month only</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
-        <is>
-          <t>Env: ttt-qa-1 with `statistic_report` populated for at least the past 12 months across a sample of employees. Access to the two test endpoints:
-  POST /api/ttt/v1/test/statistic-reports/full-sync     (full)
-  POST /api/ttt/v1/test/statistic-reports/sync          (optimized)</t>
-        </is>
-      </c>
-      <c r="D11" s="22" t="inlineStr">
-        <is>
-          <t>SETUP: Snapshot `max(updated_at)` per month for an employee with a full year of data:
-  SELECT month_start, max(updated_at) as last_updated
-  FROM ttt_backend.statistic_report
-  WHERE employee_id = &lt;chosen_emp_id&gt;
-  GROUP BY month_start ORDER BY month_start;
-Record as `snapshot_before_optimized`.
-TRIGGER (optimized): `POST /api/ttt/v1/test/statistic-reports/sync`.
-WAIT: 120 s.
-DB-CHECK (optimized scope): Re-query same SQL. Only rows for `date_trunc('month', CURRENT_DATE)` and `date_trunc('month', CURRENT_DATE - INTERVAL '1 month')` should have `updated_at` advanced; all OLDER month rows unchanged.
-SETUP (reset snapshot): Re-snapshot as `snapshot_before_full`.
-TRIGGER (full): `POST /api/ttt/v1/test/statistic-reports/full-sync`.
-WAIT: 300 s (full sync is slower — year scope).
-DB-CHECK (full scope): Re-query. ALL rows for `date_trunc('year', CURRENT_DATE)` and `date_trunc('year', CURRENT_DATE - INTERVAL '1 year')` should have `updated_at` advanced; rows older than 2 years unchanged.
-CLEANUP: None.</t>
-        </is>
-      </c>
-      <c r="E11" s="22" t="inlineStr">
-        <is>
-          <t>Optimized sync updates previous + current month rows only. Full sync updates previous + current year rows (all 12–24 months in the year scope). Rows outside each scope remain untouched (`updated_at` preserved). Confirms the two endpoints have distinct, documented effects — critical for QA's data-setup playbooks (which endpoint to call to refresh what).</t>
-        </is>
-      </c>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G11" s="21" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="H11" s="22" t="inlineStr">
-        <is>
-          <t>#3345 note 894873; #3423 row 22; EXT-cron-jobs §Session 131.4</t>
-        </is>
-      </c>
-      <c r="I11" s="22" t="inlineStr">
-        <is>
-          <t>ttt-service/statistic-report/sync</t>
-        </is>
-      </c>
-      <c r="J11" s="22" t="inlineStr">
-        <is>
-          <t>Per #3345 note 894895 (omaksimova 2026-01-07), full-sync 'NOT-A-BUG' observation: dismissed employees briefly appeared in current-year records after full sync because the scope includes them by definition. Expected behavior — do NOT assert dismissed-employee absence in full-sync scope. That assertion belongs in TC-STAT-079 (post-leave filter) only.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
